--- a/research/traditional_assets/database/data/croatia/croatia_apparel.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_apparel.xlsx
@@ -591,22 +591,22 @@
         <v>-0.0833</v>
       </c>
       <c r="G2">
-        <v>-0.4144827586206896</v>
+        <v>-0.2702127659574468</v>
       </c>
       <c r="H2">
-        <v>-0.4144827586206896</v>
+        <v>-0.2702127659574468</v>
       </c>
       <c r="I2">
-        <v>-0.3379310344827586</v>
+        <v>-0.2567375886524823</v>
       </c>
       <c r="J2">
-        <v>-0.3379310344827586</v>
+        <v>-0.2567375886524823</v>
       </c>
       <c r="K2">
-        <v>-2.57</v>
+        <v>-2.42</v>
       </c>
       <c r="L2">
-        <v>-0.1772413793103448</v>
+        <v>-0.1716312056737589</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.047</v>
+        <v>0.225</v>
       </c>
       <c r="V2">
-        <v>0.02216981132075472</v>
+        <v>0.15625</v>
       </c>
       <c r="W2">
-        <v>-1.317948717948718</v>
+        <v>-0.8402777777777778</v>
       </c>
       <c r="X2">
-        <v>0.8131107036953877</v>
+        <v>0.7824176770278708</v>
       </c>
       <c r="Y2">
-        <v>-2.131059421644106</v>
+        <v>-1.622695454805648</v>
       </c>
       <c r="Z2">
-        <v>0.5306301690697504</v>
+        <v>0.5416202512196059</v>
       </c>
       <c r="AA2">
-        <v>-0.1793164019615019</v>
+        <v>-0.1390542772634733</v>
       </c>
       <c r="AB2">
-        <v>0.1542569670456434</v>
+        <v>0.1610159158057703</v>
       </c>
       <c r="AC2">
-        <v>-0.3335733690071453</v>
+        <v>-0.3000701930692437</v>
       </c>
       <c r="AD2">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="AG2">
-        <v>23.153</v>
+        <v>20.875</v>
       </c>
       <c r="AH2">
-        <v>0.9162717219589257</v>
+        <v>0.9361135758651287</v>
       </c>
       <c r="AI2">
-        <v>0.8895705521472393</v>
+        <v>0.9664712348845731</v>
       </c>
       <c r="AJ2">
-        <v>0.9161160131365489</v>
+        <v>0.9354694151915751</v>
       </c>
       <c r="AK2">
-        <v>0.8893711827296125</v>
+        <v>0.9661220900634054</v>
       </c>
       <c r="AL2">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AM2">
-        <v>1.248</v>
+        <v>1.568</v>
       </c>
       <c r="AN2">
-        <v>-5.395348837209302</v>
+        <v>-6.698412698412699</v>
       </c>
       <c r="AO2">
-        <v>-3.92</v>
+        <v>-2.305732484076433</v>
       </c>
       <c r="AP2">
-        <v>-5.384418604651163</v>
+        <v>-6.626984126984127</v>
       </c>
       <c r="AQ2">
-        <v>-3.926282051282052</v>
+        <v>-2.308673469387755</v>
       </c>
     </row>
     <row r="3">
@@ -719,22 +719,22 @@
         <v>-0.0833</v>
       </c>
       <c r="G3">
-        <v>-0.4144827586206896</v>
+        <v>-0.2702127659574468</v>
       </c>
       <c r="H3">
-        <v>-0.4144827586206896</v>
+        <v>-0.2702127659574468</v>
       </c>
       <c r="I3">
-        <v>-0.3379310344827586</v>
+        <v>-0.2567375886524823</v>
       </c>
       <c r="J3">
-        <v>-0.3379310344827586</v>
+        <v>-0.2567375886524823</v>
       </c>
       <c r="K3">
-        <v>-2.57</v>
+        <v>-2.42</v>
       </c>
       <c r="L3">
-        <v>-0.1772413793103448</v>
+        <v>-0.1716312056737589</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.047</v>
+        <v>0.225</v>
       </c>
       <c r="V3">
-        <v>0.02216981132075472</v>
+        <v>0.15625</v>
       </c>
       <c r="W3">
-        <v>-1.317948717948718</v>
+        <v>-0.8402777777777778</v>
       </c>
       <c r="X3">
-        <v>0.8131107036953877</v>
+        <v>0.7824176770278708</v>
       </c>
       <c r="Y3">
-        <v>-2.131059421644106</v>
+        <v>-1.622695454805648</v>
       </c>
       <c r="Z3">
-        <v>0.5306301690697504</v>
+        <v>0.5416202512196059</v>
       </c>
       <c r="AA3">
-        <v>-0.1793164019615019</v>
+        <v>-0.1390542772634733</v>
       </c>
       <c r="AB3">
-        <v>0.1542569670456434</v>
+        <v>0.1610159158057703</v>
       </c>
       <c r="AC3">
-        <v>-0.3335733690071453</v>
+        <v>-0.3000701930692437</v>
       </c>
       <c r="AD3">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="AG3">
-        <v>23.153</v>
+        <v>20.875</v>
       </c>
       <c r="AH3">
-        <v>0.9162717219589257</v>
+        <v>0.9361135758651287</v>
       </c>
       <c r="AI3">
-        <v>0.8895705521472393</v>
+        <v>0.9664712348845731</v>
       </c>
       <c r="AJ3">
-        <v>0.9161160131365489</v>
+        <v>0.9354694151915751</v>
       </c>
       <c r="AK3">
-        <v>0.8893711827296125</v>
+        <v>0.9661220900634054</v>
       </c>
       <c r="AL3">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AM3">
-        <v>1.248</v>
+        <v>1.568</v>
       </c>
       <c r="AN3">
-        <v>-5.395348837209302</v>
+        <v>-6.698412698412699</v>
       </c>
       <c r="AO3">
-        <v>-3.92</v>
+        <v>-2.305732484076433</v>
       </c>
       <c r="AP3">
-        <v>-5.384418604651163</v>
+        <v>-6.626984126984127</v>
       </c>
       <c r="AQ3">
-        <v>-3.926282051282052</v>
+        <v>-2.308673469387755</v>
       </c>
     </row>
   </sheetData>
